--- a/data.xlsx
+++ b/data.xlsx
@@ -817,7 +817,11 @@
       <c r="B11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="7"/>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not applicable (three-member team)</t>
+        </is>
+      </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B12" s="6" t="s">
@@ -977,7 +981,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Civil Appeal Nos. 10820-10822 of 2014 (with C.A. 1797 of 2015)</t>
+          <t xml:space="preserve">Civil Appeal Nos. 10820-10822 of 2014 (with C.A. No. 1797 of 2015)</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1013,17 +1017,17 @@
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">s 3(3)(d) Competition Act</t>
+          <t xml:space="preserve">s 3(1) r/w s 3(3)(d) Competition Act (bid rigging); s 2(u) (service)</t>
         </is>
       </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whether CCI can look into bid rigging in lottery tenders when lotteries are res extra commercium.</t>
+          <t xml:space="preserve">Whether the CCI can inquire into bid rigging in tenders for lottery distributors when lotteries are res extra commercium.</t>
         </is>
       </c>
       <c r="M6" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. The lottery trade being regulated does not take collusive bidding outside the Act; the High Court order was set aside and the CCI inquiry continues.</t>
+          <t xml:space="preserve">Yes. The regulated status of lotteries does not take collusive tendering out of the Act; the Gauhati HC judgment was set aside and the CCI inquiry against the bidders continues (paras 43-44).</t>
         </is>
       </c>
       <c r="N6" s="12" t="inlineStr">
@@ -1053,7 +1057,7 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Civil Appeal No. 2845 of 2017</t>
+          <t xml:space="preserve">Civil Appeal No. 2845 of 2017; (2023) 10 SCC 345</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -1089,17 +1093,17 @@
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">s 4 r/w s 2(h) Competition Act</t>
+          <t xml:space="preserve">s 2(h) and s 4 r/w s 19(4)(g) Competition Act</t>
         </is>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whether the Competition Act applies to Coal India despite the Coal Mines (Nationalisation) Act and Art 39(b).</t>
+          <t xml:space="preserve">Whether the Competition Act applies to Coal India despite the Coal Mines (Nationalisation) Act, 1973 and Art 39(b).</t>
         </is>
       </c>
       <c r="M7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">It does. A government company with a statutory monopoly is an enterprise under the Act; the appeal was sent to be heard on its own merits.</t>
+          <t xml:space="preserve">It does. A government company holding a statutory monopoly is an enterprise and is not exempt; the appeal was directed to be heard on its own merits (paras 125-126).</t>
         </is>
       </c>
       <c r="N7" s="12" t="inlineStr">
@@ -1114,7 +1118,7 @@
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Madhura Kulkarni</t>
+          <t xml:space="preserve">Shreya Kotecha</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1133,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025 INSC 124 (Civil Appeal No. 6071 of 2023)</t>
+          <t xml:space="preserve">2025 INSC 124 (Civil Appeal No. 6071 of 2023 and connected appeals)</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -1165,17 +1169,17 @@
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">proviso to s 31(4) IBC; s 29 Competition Act</t>
+          <t xml:space="preserve">proviso to s 31(4) IBC r/w ss 6 and 29 Competition Act</t>
         </is>
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whether CCI approval of a combination must come before the CoC approves an insolvency resolution plan.</t>
+          <t xml:space="preserve">Whether CCI approval of a combination must be obtained before the CoC approves an insolvency resolution plan.</t>
         </is>
       </c>
       <c r="M8" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prior CCI approval is mandatory. The AGI Greenpac plan was set aside and the CoC was told to reconsider the plans.</t>
+          <t xml:space="preserve">Prior CCI approval is mandatory, not directory. The AGI Greenpac plan was quashed and the CoC directed to reconsider plans that had CCI approval (paras 155-158; S.V.N. Bhatti J. wrote separately).</t>
         </is>
       </c>
       <c r="N8" s="12" t="inlineStr">
@@ -1190,7 +1194,7 @@
       </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shankar Singh</t>
+          <t xml:space="preserve">Shreya Kotecha</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1209,7 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025 INSC 668 (Civil Appeal No. 5843 of 2014 with C.A. 9998 of 2014)</t>
+          <t xml:space="preserve">2025 INSC 668 (Civil Appeal No. 5843 of 2014 with C.A. No. 9998 of 2014)</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -1241,17 +1245,17 @@
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">s 4 Competition Act</t>
+          <t xml:space="preserve">s 4(2)(a), (b), (d) and (e) Competition Act; s 36(2) (cross-examination)</t>
         </is>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whether Schott's volume rebates, long-term supply deal and alleged tying were an abuse of dominance.</t>
+          <t xml:space="preserve">Whether Schott's volume rebates, long-term supply agreement and alleged tying were an abuse of dominant position.</t>
         </is>
       </c>
       <c r="M9" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">No abuse shown. Conduct must be judged by its actual effect on competition, and the DG probe was flawed because cross-examination was refused.</t>
+          <t xml:space="preserve">No abuse established. An effects-based analysis is obligatory in every s 4 inquiry (para 66(i)), and refusing cross-examination vitiated the DG's findings (paras 75, 77); appeals dismissed (para 79).</t>
         </is>
       </c>
       <c r="N9" s="12" t="inlineStr">
@@ -1276,7 +1280,7 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Competition Commission of India v. Independent Sugar Corporation Ltd. &amp; Anr. (review)</t>
+          <t xml:space="preserve">Competition Commission of India v. Independent Sugar Corporation Ltd. &amp; Anr.</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -1317,17 +1321,17 @@
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">s 29 Competition Act</t>
+          <t xml:space="preserve">s 29(1) and s 29(1A) Competition Act; Reg 25(1A) Combination Regulations</t>
         </is>
       </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whether s 29 forces the CCI to send every combination to the DG after a show cause notice.</t>
+          <t xml:space="preserve">Whether s 29 requires the CCI to send every combination to the DG after issuing a show cause notice.</t>
         </is>
       </c>
       <c r="M10" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">No. The notice under s 29(1) is mandatory, but a DG reference under s 29(1A) is the CCI's choice; paras 128-131 of the January judgment were replaced.</t>
+          <t xml:space="preserve">No. A show cause notice under s 29(1) is mandatory, but a DG reference under s 29(1A) is discretionary; paras 128-131 of the 29-01-2025 judgment were replaced by paras 10-11 of the review order.</t>
         </is>
       </c>
       <c r="N10" s="12" t="inlineStr">
@@ -1342,7 +1346,7 @@
       </c>
       <c r="P10" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Madhura Kulkarni</t>
+          <t xml:space="preserve">Shreya Kotecha</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1361,7 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">SLP(C) No. 25026 of 2023 and connected SLPs</t>
+          <t xml:space="preserve">SLP(C) No. 25026 of 2023 with SLP(C) Nos. 12209, 6934, 5871 and 5870 of 2024</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -1393,22 +1397,22 @@
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">s 26(1) Competition Act</t>
+          <t xml:space="preserve">s 26(1) Competition Act; Patents Act, 1970</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whether the CCI probe into patent licensing terms could go on after the informants settled with the patentees.</t>
+          <t xml:space="preserve">Whether the CCI probe into patent licensing terms could continue after the informants settled with the patentees.</t>
         </is>
       </c>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Court refused to interfere with the Delhi HC order quashing the probe, as the settlement removed its basis; the Patents Act v. Competition Act question was kept open.</t>
+          <t xml:space="preserve">The Court declined to interfere with the Delhi HC judgment of 13-07-2023, accepting that the settlement removed the substratum of the probe, and kept the Patents Act versus Competition Act question open.</t>
         </is>
       </c>
       <c r="N11" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">None cited; rests on Delhi HC judgment in Telefonaktiebolaget LM Ericsson v. CCI (13-07-2023)</t>
+          <t xml:space="preserve">Telefonaktiebolaget LM Ericsson v. CCI (Delhi HC, LPA 247 of 2016, 13-07-2023), para 58</t>
         </is>
       </c>
       <c r="O11" s="12" t="inlineStr">
@@ -1418,7 +1422,7 @@
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shankar Singh</t>
+          <t xml:space="preserve">Shreya Kotecha</t>
         </is>
       </c>
     </row>
@@ -1469,22 +1473,22 @@
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">s 3(3)(b) r/w s 27 and s 48 Competition Act</t>
+          <t xml:space="preserve">s 3(1) r/w s 3(3)(b), s 27 and s 48 Competition Act (pre-2023 text)</t>
         </is>
       </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whether office-bearers of a trade body needed a second show cause notice before penalty, and whether the penalty was excessive.</t>
+          <t xml:space="preserve">Whether office-bearers of a trade association were entitled to a second show cause notice on penalty, and whether the penalty was disproportionate.</t>
         </is>
       </c>
       <c r="M12" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">One notice was enough and the penalty was proportionate. The CCI order, including the two-year bar on the office-bearers, was restored.</t>
+          <t xml:space="preserve">One notice was enough and the penalty was proportionate (paras 52, 64). The COMPAT order was set aside and the CCI order of 08-09-2015, including the two-year bar on the office-bearers, was restored (para 68).</t>
         </is>
       </c>
       <c r="N12" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CCI v. Steel Authority of India Ltd. (2010) 10 SCC 744</t>
+          <t xml:space="preserve">Excel Crop Care Ltd. v. CCI (2017) 8 SCC 47</t>
         </is>
       </c>
       <c r="O12" s="12" t="inlineStr">
@@ -1504,7 +1508,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flipkart India Pvt. Ltd. &amp; Anr. v. Competition Commission of India &amp; Ors.</t>
+          <t xml:space="preserve">Flipkart India Pvt. Ltd. &amp; Anr. v. Competition Commission of India &amp; Anr.</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -1545,32 +1549,32 @@
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">s 4 r/w s 26(1) Competition Act</t>
+          <t xml:space="preserve">s 4 r/w s 26(1) and s 53B Competition Act</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whether the NCLAT's direction for a DG probe into Flipkart could stand once the tax findings it relied on were set aside by the ITAT.</t>
+          <t xml:space="preserve">Whether the NCLAT's direction for a DG investigation into Flipkart could stand when it rested on an income tax assessment order no longer in existence.</t>
         </is>
       </c>
       <c r="M13" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">NCLAT order set aside and the appeal sent back to the NCLAT to decide afresh whether a prima facie case exists, applying Coal India.</t>
+          <t xml:space="preserve">Appeal allowed in part. The NCLAT order of 04-03-2020 was set aside and the appeal remanded for fresh decision on whether a prima facie case exists, applying Coal India; no view on merits.</t>
         </is>
       </c>
       <c r="N13" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coal India Ltd. v. CCI (2023)</t>
+          <t xml:space="preserve">Coal India Ltd. v. CCI (2023) 10 SCC 345</t>
         </is>
       </c>
       <c r="O13" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.sci.gov.in/judgements-case-no/ (search C.A. 2770/2020, order dated 03-02-2026)</t>
+          <t xml:space="preserve">https://api.sci.gov.in/supremecourt/2020/10296/10296_2020_1_16_67887_Order_03-Feb-2026.pdf</t>
         </is>
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Madhura Kulkarni</t>
+          <t xml:space="preserve">Shreya Kotecha</t>
         </is>
       </c>
     </row>
@@ -1621,22 +1625,22 @@
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">s 45(2) r/w s 20(1) and s 31(1) Competition Act</t>
+          <t xml:space="preserve">s 45(2) r/w proviso to s 20(1), s 31(1), ss 43A and 44 Competition Act; Reg 5(5) Combination Regulations</t>
         </is>
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whether the CCI could keep its 2019 approval of the Amazon-Future Coupons deal in abeyance and impose penalties for non-disclosure.</t>
+          <t xml:space="preserve">Whether the CCI could hold its 2019 approval of the Amazon-Future Coupons combination in abeyance and impose penalties for incomplete disclosure.</t>
         </is>
       </c>
       <c r="M14" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">No. s 45(2) is a penal provision, not a review power; the action was also out of time under s 20(1). CCI and NCLAT orders set aside and penalties to be refunded.</t>
+          <t xml:space="preserve">No. s 45(2) is a penal provision and gives no power to suspend or reopen an approval, and the action was outside the one-year limit in s 20(1). The NCLAT and CCI orders were set aside and deposits ordered refunded with 6% interest (paras 303-305).</t>
         </is>
       </c>
       <c r="N14" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangalore Chemicals &amp; Fertilisers Ltd. v. Dy. Commissioner of Commercial Taxes (1992)</t>
+          <t xml:space="preserve">Gorkha Security Services v. Govt. (NCT of Delhi) (2014) 9 SCC 105</t>
         </is>
       </c>
       <c r="O14" s="12" t="inlineStr">
@@ -1646,7 +1650,7 @@
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shankar Singh</t>
+          <t xml:space="preserve">Shreya Kotecha</t>
         </is>
       </c>
     </row>
